--- a/output.xlsx
+++ b/output.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="AZ_comp" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Trimming" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,78 +436,64 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>measure_values</t>
+          <t>Best Codes</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Closest Values</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3rd_STG_Current</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>9.781278179999999e-07</v>
+          <t>VBGR_ADJ_TRIM</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4E</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1.797901115</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2nd_STG_Current</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.4452246e-06</v>
+          <t>TSDN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5399711</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1st_STG_Current</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>8.08875571e-07</v>
+          <t>FRO_CLOCK</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ground_AZCOMP</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.125428e-05</v>
+          <t>BST_OCP_TRIM_reg1</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OUTN_EXT_PRT</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.00368484</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>OUTP_EXT_PRT</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.005984325</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>VCM_AVDD</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.804062855</v>
+          <t>BST_OCP_TRIM_reg2</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/output.xlsx
+++ b/output.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.797901115</v>
+        <v>1.798300865</v>
       </c>
     </row>
     <row r="3">
@@ -468,11 +468,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>9F</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.5399711</v>
+        <v>0.54319288125</v>
       </c>
     </row>
     <row r="4">
@@ -481,6 +481,14 @@
           <t>FRO_CLOCK</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>817225.1799999999</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -488,11 +496,24 @@
           <t>BST_OCP_TRIM_reg1</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7F</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7223611544999999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>BST_OCP_TRIM_reg2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>F0</t>
         </is>
       </c>
     </row>
